--- a/objects/recent_cancer_treatment.xlsx
+++ b/objects/recent_cancer_treatment.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t xml:space="preserve">model</t>
   </si>
@@ -23,6 +23,9 @@
     <t xml:space="preserve">term</t>
   </si>
   <si>
+    <t xml:space="preserve">Severe COVID</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hospitalized</t>
   </si>
   <si>
@@ -38,202 +41,253 @@
     <t xml:space="preserve">Chemotherapy</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11 (3.58, 4.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04 (2.38, 3.88)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59 (4.31, 7.25)</t>
+    <t xml:space="preserve">4.48 (3.96, 5.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17 (3.67, 4.73)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09 (2.44, 3.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62 (4.40, 7.18)</t>
   </si>
   <si>
     <t xml:space="preserve">unadjusted_firth</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05 (2.37, 3.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62 (4.31, 7.24)</t>
+    <t xml:space="preserve">3.10 (2.44, 3.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65 (4.40, 7.17)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79 (2.42, 3.22)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04 (1.57, 2.60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87 (2.18, 3.73)</t>
+    <t xml:space="preserve">2.96 (2.60, 3.36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82 (2.47, 3.22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07 (1.61, 2.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85 (2.21, 3.65)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92 (2.50, 3.40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03 (1.54, 2.64)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69 (1.99, 3.58)</t>
+    <t xml:space="preserve">2.97 (2.58, 3.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93 (2.54, 3.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11 (1.62, 2.72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48 (1.85, 3.25)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99 (2.54, 3.51)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57 (1.92, 3.39)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90 (2.12, 3.90)</t>
+    <t xml:space="preserve">2.99 (2.58, 3.45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97 (2.55, 3.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65 (2.02, 3.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57 (1.91, 3.41)</t>
   </si>
   <si>
     <t xml:space="preserve">No treatment/Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55 (1.37, 1.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36 (1.07, 1.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04 (2.41, 3.84)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56 (1.37, 1.76)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37 (1.07, 1.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06 (2.41, 3.83)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97 (0.85, 1.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86 (0.67, 1.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35 (1.06, 1.71)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98 (0.85, 1.13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88 (0.67, 1.13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35 (1.04, 1.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.09 (0.93, 1.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13 (0.85, 1.49)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48 (1.11, 1.94)</t>
+    <t xml:space="preserve">1.71 (1.53, 1.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55 (1.38, 1.75)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37 (1.09, 1.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08 (2.48, 3.83)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55 (1.37, 1.75)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09 (2.48, 3.82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04 (0.93, 1.17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.98 (0.87, 1.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87 (0.69, 1.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39 (1.10, 1.73)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02 (0.90, 1.16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96 (0.84, 1.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85 (0.66, 1.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30 (1.01, 1.65)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10 (0.96, 1.26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05 (0.91, 1.21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08 (0.81, 1.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42 (1.09, 1.83)</t>
   </si>
   <si>
     <t xml:space="preserve">Radiation Only</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35 (2.43, 4.62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99 (1.73, 5.15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28 (3.69, 10.69)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38 (2.43, 4.61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09 (1.73, 5.08)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47 (3.68, 10.56)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92 (1.37, 2.65)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70 (0.95, 2.84)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62 (1.47, 4.34)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93 (1.33, 2.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60 (0.82, 2.81)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55 (1.34, 4.43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11 (1.44, 3.04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03 (1.01, 3.66)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31 (1.13, 4.22)</t>
+    <t xml:space="preserve">3.38 (2.51, 4.54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19 (2.34, 4.34)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89 (1.68, 4.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63 (4.02, 10.92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40 (2.51, 4.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21 (2.33, 4.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98 (1.67, 4.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80 (4.01, 10.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80 (1.32, 2.42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78 (1.28, 2.42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62 (0.90, 2.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62 (1.53, 4.22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72 (1.22, 2.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71 (1.19, 2.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49 (0.77, 2.61)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49 (1.37, 4.18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74 (1.21, 2.45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80 (1.24, 2.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83 (0.91, 3.29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20 (1.15, 3.86)</t>
   </si>
   <si>
     <t xml:space="preserve">Surgery Only</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69 (1.03, 7.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63 (0.22, 11.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00 (0.00, 40552418076145502790882578786987113236548241140070130389513528358351915132865400942250209506632794577800876701147189324967743324160.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90 (1.03, 6.75)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40 (0.27, 9.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51 (0.01, 10.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80 (0.63, 4.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49 (0.17, 5.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.67 (0.01, 4.94)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91 (0.66, 4.63)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45 (0.16, 5.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.63 (0.00, 4.80)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65 (0.56, 4.12)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56 (0.17, 6.28)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.49 (0.00, 3.89)</t>
+    <t xml:space="preserve">2.40 (0.93, 6.21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61 (1.01, 6.75)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67 (0.23, 12.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (0.00, 35558966735938140934143815501065987800089201745874448409994072186047574918447041441076018859723329772465733749224883703775232.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60 (0.93, 5.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82 (1.01, 6.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47 (0.28, 9.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50 (0.01, 10.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59 (0.56, 3.74)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80 (0.64, 4.24)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59 (0.18, 6.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.68 (0.01, 4.99)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66 (0.58, 3.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90 (0.66, 4.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55 (0.17, 6.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.64 (0.00, 4.77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43 (0.49, 3.52)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67 (0.57, 4.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69 (0.19, 6.77)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50 (0.00, 3.89)</t>
   </si>
 </sst>
 </file>
@@ -578,90 +632,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -691,90 +763,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -804,90 +894,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>56</v>
+      </c>
+      <c r="F3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="F4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>64</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>68</v>
+      </c>
+      <c r="F6" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -917,90 +1025,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>73</v>
+      </c>
+      <c r="F2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>81</v>
+      </c>
+      <c r="F4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>85</v>
+      </c>
+      <c r="F5" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>89</v>
+      </c>
+      <c r="F6" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/objects/recent_cancer_treatment.xlsx
+++ b/objects/recent_cancer_treatment.xlsx
@@ -65,43 +65,43 @@
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96 (2.60, 3.36)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82 (2.47, 3.22)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07 (1.61, 2.61)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85 (2.21, 3.65)</t>
+    <t xml:space="preserve">2.98 (2.62, 3.39)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85 (2.49, 3.25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05 (1.61, 2.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84 (2.19, 3.63)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97 (2.58, 3.41)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93 (2.54, 3.38)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11 (1.62, 2.72)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48 (1.85, 3.25)</t>
+    <t xml:space="preserve">3.00 (2.61, 3.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96 (2.56, 3.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11 (1.62, 2.71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47 (1.85, 3.25)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99 (2.58, 3.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97 (2.55, 3.44)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65 (2.02, 3.44)</t>
+    <t xml:space="preserve">3.00 (2.60, 3.46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99 (2.57, 3.46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67 (2.03, 3.47)</t>
   </si>
   <si>
     <t xml:space="preserve">2.57 (1.91, 3.41)</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">1.02 (0.90, 1.16)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.96 (0.84, 1.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.85 (0.66, 1.09)</t>
+    <t xml:space="preserve">0.97 (0.84, 1.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.85 (0.65, 1.09)</t>
   </si>
   <si>
     <t xml:space="preserve">1.30 (1.01, 1.65)</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">1.10 (0.96, 1.26)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05 (0.91, 1.21)</t>
+    <t xml:space="preserve">1.05 (0.90, 1.21)</t>
   </si>
   <si>
     <t xml:space="preserve">1.08 (0.81, 1.41)</t>
@@ -191,40 +191,40 @@
     <t xml:space="preserve">6.80 (4.01, 10.80)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80 (1.32, 2.42)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78 (1.28, 2.42)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62 (0.90, 2.68)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62 (1.53, 4.22)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72 (1.22, 2.38)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71 (1.19, 2.39)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49 (0.77, 2.61)</t>
+    <t xml:space="preserve">1.81 (1.33, 2.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79 (1.29, 2.44)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61 (0.90, 2.67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61 (1.52, 4.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73 (1.23, 2.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72 (1.20, 2.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49 (0.77, 2.60)</t>
   </si>
   <si>
     <t xml:space="preserve">2.49 (1.37, 4.18)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74 (1.21, 2.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80 (1.24, 2.56)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83 (0.91, 3.29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20 (1.15, 3.86)</t>
+    <t xml:space="preserve">1.75 (1.22, 2.46)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81 (1.24, 2.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84 (0.91, 3.31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21 (1.15, 3.86)</t>
   </si>
   <si>
     <t xml:space="preserve">Surgery Only</t>
@@ -254,40 +254,40 @@
     <t xml:space="preserve">1.50 (0.01, 10.56)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59 (0.56, 3.74)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80 (0.64, 4.24)</t>
+    <t xml:space="preserve">1.59 (0.56, 3.73)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80 (0.64, 4.22)</t>
   </si>
   <si>
     <t xml:space="preserve">1.59 (0.18, 6.13)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68 (0.01, 4.99)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66 (0.58, 3.98)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90 (0.66, 4.56)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55 (0.17, 6.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.64 (0.00, 4.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43 (0.49, 3.52)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67 (0.57, 4.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69 (0.19, 6.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50 (0.00, 3.89)</t>
+    <t xml:space="preserve">0.68 (0.01, 4.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66 (0.58, 3.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90 (0.66, 4.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55 (0.17, 6.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63 (0.00, 4.76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42 (0.49, 3.49)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66 (0.57, 4.07)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70 (0.19, 6.78)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50 (0.00, 3.90)</t>
   </si>
 </sst>
 </file>
